--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T3_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.264</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>0.418</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>0.165</t>
-  </si>
-  <si>
-    <t>(0.039)</t>
-  </si>
-  <si>
-    <t>0.648</t>
-  </si>
-  <si>
-    <t>(0.184)</t>
-  </si>
-  <si>
-    <t>0.912</t>
-  </si>
-  <si>
-    <t>(0.165)</t>
-  </si>
-  <si>
-    <t>0.209</t>
-  </si>
-  <si>
-    <t>(0.060)</t>
+    <t>0.276</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>0.437</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>0.172</t>
+  </si>
+  <si>
+    <t>(0.041)</t>
+  </si>
+  <si>
+    <t>0.678</t>
+  </si>
+  <si>
+    <t>(0.192)</t>
+  </si>
+  <si>
+    <t>0.954</t>
+  </si>
+  <si>
+    <t>(0.171)</t>
+  </si>
+  <si>
+    <t>0.218</t>
+  </si>
+  <si>
+    <t>(0.062)</t>
   </si>
   <si>
     <t>23</t>
@@ -135,7 +135,7 @@
     <t>(0.174)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -147,22 +147,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.171</t>
-  </si>
-  <si>
-    <t>0.409***</t>
-  </si>
-  <si>
-    <t>0.444***</t>
-  </si>
-  <si>
-    <t>0.830</t>
-  </si>
-  <si>
-    <t>2.001***</t>
-  </si>
-  <si>
-    <t>0.617***</t>
+    <t>0.159</t>
+  </si>
+  <si>
+    <t>0.389***</t>
+  </si>
+  <si>
+    <t>0.436***</t>
+  </si>
+  <si>
+    <t>0.800</t>
+  </si>
+  <si>
+    <t>1.959***</t>
+  </si>
+  <si>
+    <t>0.608***</t>
   </si>
 </sst>
 </file>
